--- a/sensores-finca.xlsx
+++ b/sensores-finca.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -566,16 +566,16 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Lote B · Mango</t>
+          <t>Lote A · Cacao</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Humedad</t>
+          <t>Humedad de suelo</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -596,20 +596,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Lote C · Café</t>
+          <t>Lote A · Cacao</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Humedad</t>
+          <t>Temperatura</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Lote D · Cacao</t>
+          <t>Lote B · Mango</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>aviso</t>
+          <t>alerta</t>
         </is>
       </c>
     </row>
@@ -656,25 +656,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Vivero</t>
+          <t>Lote B · Mango</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temperatura</t>
+          <t>Humedad de suelo</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
     </row>
@@ -686,75 +686,315 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Lote B · Mango</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>S-07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Lote C · Café</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>S-08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Lote C · Café</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Humedad de suelo</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>S-09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Lote C · Café</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Lote D · Cacao</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Lote D · Cacao</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Humedad de suelo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S-12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Lote D · Cacao</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S-13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Vivero</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>S-14</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>Zona hídrica</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Caudal riego</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>l/m</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>sin señal</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -772,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -833,43 +1073,50 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Vivero, Zona hídrica). 'tipo' es lo que mide (Humedad, Temperatura, etc).</t>
+          <t xml:space="preserve">   Vivero, Zona hídrica). Cada Lote tiene 3 filas, una por 'tipo': Humedad,</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>6. Para agregar un sensor nuevo, usa una fila vacía y completa las 6 columnas.</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Humedad de suelo y Temperatura.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
+          <t>6. Para agregar un sensor nuevo, usa una fila vacía y completa las 6 columnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
           <t>7. No hace falta guardar nada especial — Google Sheets guarda solo.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>El sitio web lee esta hoja automáticamente cada pocos minutos.</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Si algo se ve raro en la web, revisa que 'estado' tenga exactamente una de esas</t>
+          <t>El sitio web lee esta hoja automáticamente cada pocos minutos.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Si algo se ve raro en la web, revisa que 'estado' tenga exactamente una de esas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>cuatro palabras y que 'valor' sea un número.</t>
         </is>
